--- a/extenbooks/S1502_extenbook.xlsx
+++ b/extenbooks/S1502_extenbook.xlsx
@@ -6515,7 +6515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -7800,11 +7800,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7827,64 +7827,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Chapter 15 series S1502</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S1502_research.json", "adequacy_report": "Technical/docs/chapters/CH15_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S1502_DPR.md", "epr": "Technical/docs/series/S1502_EPR.md", "loader": "Technical/code/L01_loaders/L01_S1502_load.py", "processor": "Technical/code/P02_processors/P02_S1502_construct.py", "validator": "Technical/code/V03_validators/V03_S1502_validate.py", "processed": "Technical/data/processed/S1502.parquet", "chopped_csv": "Technical/chopped/S1502.csv", "extenbook_xlsx": "Technical/extenbooks/S1502_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S1502_extenbook.xlsx
+++ b/extenbooks/S1502_extenbook.xlsx
@@ -848,7 +848,7 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2421,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4077,7 +4077,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>rate_decimal_log_diff</t>
+          <t>decimal_annual_growth_rate</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A123"/>
+  <dimension ref="A1:A129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -6501,7 +6501,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Pipeline stage**: Ingestion</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -6661,31 +6661,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Publisher / Series ID | Native units | Retrieval |</t>
+          <t>*Each series is built from sub-components identified by a suffix on the series ID (for example, S1502-A, S1502-B); they are listed below.*</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| **S1502-A** through **S1502-I** | 1988-2010 (book period) | BEA GDP-by-Industry program, Chain-Type Quantity Indexes for Gross Output by Industry (2005=100 vintage) | Rate (decimal, log-difference) | Salvaged chopped table `Appendix15_USGDPRByIndustry.xlsx` sheet `Data`, "Calculated Growth Rate" columns |</t>
+          <t>| Subseries | Coverage | Publisher / Series ID | Native units | Retrieval |</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>|---|---|---|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Each industry has its own subseries ID; details in the registry. The "All industries" series is `S1502-ALL` (reference benchmark).</t>
+          <t>| **S1502-A** through **S1502-I** | 1988-2010 (book period) | BEA GDP-by-Industry program, Chain-Type Quantity Indexes for Gross Output by Industry (2005=100 vintage) | Rate (decimal, simple percent change) | Salvaged chopped table `Appendix15_USGDPRByIndustry.xlsx` sheet `Data`, "Calculated Growth Rate" columns |</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6695,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>## 4. Construction</t>
+          <t>Each industry has its own subseries ID; details in the registry. The "All industries" series is `S1502-ALL` (reference benchmark).</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S1502 is **formula** (Anu sense): `g_i(t) = (YR_i(t) - YR_i(t-1)) / YR_i(t-1)` per industry per year. The chopped table contains both the chain-type quantity index levels (cols 1-19) and Shaikh's precomputed growth rates (cols 20-38) — the loader reads BOTH and the processor recomputes growth rates from the levels using simple percent change to match Shaikh's convention.</t>
+          <t>## 4. Construction</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>**Year boundary**: 1987 is the first level year; 1988 is the first growth-rate year (per adequacy review remediation).</t>
+          <t>S1502 is **formula** (in this project's construction taxonomy): `g_i(t) = (YR_i(t) - YR_i(t-1)) / YR_i(t-1)` per industry per year. The chopped table contains both the chain-type quantity index levels (cols 1-19) and Shaikh's precomputed growth rates (cols 20-38) — the loader reads BOTH and the processor recomputes growth rates from the levels using simple percent change to match Shaikh's convention.</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>**Year boundary**: 1987 is the first level year; 1988 is the first growth-rate year (per adequacy review remediation).</t>
         </is>
       </c>
     </row>
@@ -6735,31 +6735,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>- **Book period**: 1988-2010 (annual) — 23 obs per industry</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>- **Extension period**: 2011-2025 (BEA Industry API) — feasible but requires BEA API integration; this fanout publishes book-period growth rates and marks extension as `api_key_missing` if BEA_API_KEY not set</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>- **Sector boundary caveat**: BEA NAICS reaggregations (Information sector, Federal Government NIPA reclassification ~2018) complicate post-2017 splice; documented in EPR.</t>
+          <t>- **Book period**: 1988-2010 (annual) — 23 obs per industry</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>- **Extension period**: 2011-2025 (BEA Industry API) — feasible but requires BEA API integration; this build publishes book-period growth rates and marks extension as `api_key_missing` if BEA_API_KEY not set</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>- **Sector boundary caveat**: BEA North American Industry Classification System (NAICS) reaggregations (Information sector, National Income and Product Accounts (NIPA) Federal Government reclassification ~2018) complicate post-2017 splice; documented in the Extension Provenance Record.</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>- **S1502 (final)**: Rate (decimal annual log-difference of real value added / gross output chain quantity index).</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -6779,180 +6779,188 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>- **S1502 (final)**: Rate (decimal annual **simple percent change** of the real gross output chain-type</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  quantity index): `g_i(t) = (YR_i(t) - YR_i(t-1)) / YR_i(t-1)`. Registry/chopped units string:</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1. **Vintage stability**: BEA periodically revises base year (2005=100 at Shaikh's retrieval; modern vintage 2017=100). Growth rates are scale-invariant under base rebasing, so the rates are comparable across vintages.</t>
+          <t xml:space="preserve">  `decimal_annual_growth_rate` (same vocabulary as S1401-B). NOT a log-difference — hand-verified:</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2. **1987 missing**: 1987 is the level base — growth rate begins 1988.</t>
+          <t xml:space="preserve">  DURMFG 1988 = 0.063481 = simple percent change = book precomputed 0.06348 (log-diff would be 0.061547).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3. **NAICS sector boundaries**: BEA reaggregated some sub-sectors (FIRE, Federal Gov) in revisions after 2010. The book panel uses Shaikh's 2012 vintage; post-2010 extension must splice carefully.</t>
+          <t xml:space="preserve">  Units label corrected from `rate_decimal_log_diff` in remediation T1.7 (C567, 2026-07-01).</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>4. **No proxy**: same BEA Industry source as Shaikh.</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>## 7. Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>## 8. Cross-references</t>
-        </is>
-      </c>
+      <c r="A64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1. **Vintage stability**: BEA periodically revises base year (2005=100 at Shaikh's retrieval; modern vintage 2017=100). Growth rates are scale-invariant under base rebasing, so the rates are comparable across vintages.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: `S077` (predecessor)</t>
+          <t>2. **1987 missing**: 1987 is the level base — growth rate begins 1988.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 15, Figures 15.2-15.3; Appendix 15.1 p. 895</t>
+          <t>3. **NAICS sector boundaries**: BEA reaggregated some sub-sectors (FIRE, Federal Gov) in revisions after 2010. The book panel uses Shaikh's 2012 vintage; post-2010 extension must splice carefully.</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4. **No proxy**: same BEA Industry source as Shaikh.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>## 9. Validation expectation</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>## 8. Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>- **Tolerance**: +/- 1.0% per (year, industry) on overlap 1988-2010 against book's "Calculated Growth Rate" columns.</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>- **Expected MAE**: near zero (we recompute the same log-difference formula on the same level inputs).</t>
-        </is>
-      </c>
+          <t>- **Predecessor-build ID**: `S077` (predecessor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>- **Book reference**: Shaikh (2016), Ch. 15, Figures 15.2-15.3; Appendix 15.1 p. 895</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>- **Tolerance**: +/- 1.0% per (year, industry) on overlap 1988-2010 against book's "Calculated Growth Rate" columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>- **Expected mean absolute error (MAE)**: near zero (we recompute the same simple-percent-change formula on the same level inputs).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4">
         <f>== EPR: S1502_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t># S1502 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>**Series**: S1502 — Growth Rates of Real Output, US Major Industries (Panel A)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `formula`</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>**Extension method**: re-fetch BEA Chain-Type Quantity Index for Gross Output by Industry (modern vintage), recompute `g_i(t) = ln(YR_i(t)) - ln(YR_i(t-1))` for years 2011-present, splice on growth rates (which are scale-invariant under base rebasing)</t>
-        </is>
-      </c>
-    </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t># S1502 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>**Author**: opus-subagent-fanout-ch15</t>
-        </is>
-      </c>
+      <c r="A83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>**Series**: S1502 — Growth Rates of Real Output, US Major Industries (Panel A)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Pipeline stage**: Extension</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>**Construction classification**: `formula`</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>## 1. Why this series is extendable</t>
+          <t>**Extension method**: re-fetch BEA Chain-Type Quantity Index for Gross Output by Industry (modern vintage), recompute `g_i(t) = (YR_i(t) - YR_i(t-1)) / YR_i(t-1)` (simple percent change, the book's convention — see the Data Provenance Record units correction of 2026-07-01) for years 2011-present, splice on growth rates (which are scale-invariant under base rebasing)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>S1502 is a `time_series` series of construction `formula`. Per Anu rule, extending a formula series requires re-fetching the formula's components and recomputing — that is what we do here (BEA Industry chain indices remain published; modern vintage 2017=100).</t>
+          <t>**Author**: RSCD replication pipeline (automated)</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6970,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -6972,103 +6980,103 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## 1. Why this series is extendable</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>INPUTS</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">  S1502_book = per-industry growth rates 1988-2010 from chopped table</t>
+          <t>S1502 is a `time_series` series of construction `formula`. Per this project's extension rule, extending a formula series requires re-fetching the formula's components and recomputing — that is what we do here (BEA Industry chain indices remain published; modern vintage 2017=100).</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  BEA_GDP_BY_INDUSTRY (modern vintage) = chain-type quantity indices, levels, 1987-present</t>
-        </is>
-      </c>
+      <c r="A96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>## 2. Method</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>EXTENSION</t>
-        </is>
-      </c>
+      <c r="A98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">  For each industry i and year t in [2011, current_year]:</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">    g_i(t) = ln(YR_i(t)) - ln(YR_i(t-1))</t>
+          <t>INPUTS</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Splice point: 2010 end of book period; 2011+ from BEA modern vintage.</t>
+          <t xml:space="preserve">  S1502_book = per-industry growth rates 1988-2010 from chopped table</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Because growth rates are invariant under base-year rebasing, no scale factor is required.</t>
+          <t xml:space="preserve">  BEA_GDP_BY_INDUSTRY (modern vintage) = chain-type quantity indices, levels, 1987-present</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="A103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>EXTENSION</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>## 3. No-proxy disclosure</t>
+          <t xml:space="preserve">  For each industry i and year t in [2011, current_year]:</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    g_i(t) = (YR_i(t) - YR_i(t-1)) / YR_i(t-1)   # simple percent change, the book's convention</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>**None.** Same BEA GDP-by-Industry source as the book.</t>
+          <t xml:space="preserve">  Splice point: 2010 end of book period; 2011+ from BEA modern vintage.</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Because growth rates are invariant under base-year rebasing, no scale factor is required.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>## 4. No-synthetic disclosure</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7086,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>**None.** NaNs propagate. Missing industries (e.g., NAICS reaggregations creating new sector codes) are skipped, not filled.</t>
+          <t>## 3. No-proxy disclosure</t>
         </is>
       </c>
     </row>
@@ -7088,7 +7096,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>## 5. Failure-mode table</t>
+          <t>**None.** Same BEA GDP-by-Industry source as the book.</t>
         </is>
       </c>
     </row>
@@ -7098,35 +7106,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Action |</t>
+          <t>## 4. No-synthetic disclosure</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>|---|---|---|</t>
-        </is>
-      </c>
+      <c r="A116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>| `BEA_API_KEY` not set | `S00_config` flags | Loader returns degraded; processor publishes book period only (1988-2010); registry stamped `extension_status: api_key_missing` |</t>
+          <t>**None.** NaNs propagate. Missing industries (e.g., North American Industry Classification System (NAICS) reaggregations creating new sector codes) are skipped, not filled.</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>| BEA Industry table schema changed | Loader matches industry labels rather than ordinal positions | Mismatched/dropped industries logged as warnings; never silently substituted |</t>
-        </is>
-      </c>
+      <c r="A118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>| NAICS reaggregation | Per-industry growth_rate splice | Documented per-industry in registry; affected industries flagged |</t>
+          <t>## 5. Failure-mode table</t>
         </is>
       </c>
     </row>
@@ -7136,17 +7136,55 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>## 6. CD2 divergence pre-disclosure</t>
+          <t>| Failure | Detection | Action |</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>|---|---|---|</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CD2 used the same BEA Industry source. Pre-2010 growth rates expected to match within rounding; post-2010 may diverge by ~1-3% in some industries due to NAICS reaggregation.</t>
+          <t>| `BEA_API_KEY` not set | `S00_config` flags | Loader returns degraded; processor publishes book period only (1988-2010); registry stamped `extension_status: api_key_missing` |</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>| BEA Industry table schema changed | Loader matches industry labels rather than ordinal positions | Mismatched/dropped industries logged as warnings; never silently substituted |</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>| NAICS reaggregation | Per-industry growth_rate splice | Documented per-industry in registry; affected industries flagged |</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>## 6. Divergence from the predecessor build</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>The predecessor build used the same BEA Industry source. Pre-2010 growth rates expected to match within rounding; post-2010 may diverge by ~1-3% in some industries due to NAICS reaggregation.</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7823,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:14:07.879575+00:00</t>
+          <t>2026-07-02T06:19:34.061017+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S1502_extenbook.xlsx
+++ b/extenbooks/S1502_extenbook.xlsx
@@ -7823,7 +7823,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:19:34.061017+00:00</t>
+          <t>2026-07-11T03:44:23.287127+00:00</t>
         </is>
       </c>
     </row>
@@ -7838,11 +7838,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7865,6 +7865,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BEA_GDP_BY_INDUSTRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful formula replication of book figure 15.2A (goods-producing and trade industries panel). Simple-percent-change growth rates (hand-verified: DURMFG 1988 = 0.063481 = simple pct, not log-diff) of BEA real value added by industry. Data covers 1988-2010 (first valid growth year is 1988 given a 1987 level base; book caption reads 1987-2010 - documented, not an error). Units decimal_annual_growth_rate consistent across all subseries.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1502_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S1502_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>decimal_annual_growth_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
